--- a/qa/BadGolf_CodeReviewQueue_Open_Items_2026-09-01.xlsx
+++ b/qa/BadGolf_CodeReviewQueue_Open_Items_2026-09-01.xlsx
@@ -12,10 +12,12 @@
     <sheet name="Kevin - To Do" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Fixed By Us" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Verified Closed" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Shared Maps" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Fixed By Us'!$A$4:$H$9</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Kevin - To Do'!$A$4:$I$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Shared Maps'!$A$4:$F$21</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Verified Closed'!$A$4:$E$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="360">
   <si>
     <t xml:space="preserve">Bad Golf — Code Review Queue status</t>
   </si>
@@ -60,7 +62,7 @@
     <t xml:space="preserve">Rejected / sent back</t>
   </si>
   <si>
-    <t xml:space="preserve">189 genuine mis-flags and duplicates, plus the 5 reopened today and returned to Kevin.</t>
+    <t xml:space="preserve">Historical FILINGS, not open items — breakdown below. They span 173 distinct courses.</t>
   </si>
   <si>
     <t xml:space="preserve">Still NEW (open on Kevin's list)</t>
@@ -87,6 +89,27 @@
     <t xml:space="preserve">23 flags came in; 22 resolved, 1 deliberately held.</t>
   </si>
   <si>
+    <t xml:space="preserve">Of those 194 rejected filings:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; superseded by a later entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A later filing on the same course says resolved. Closed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; still the latest word on their course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 5 reopened today, plus 1 batch entry with NO course attached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -&gt; filings with no course attached</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannot render on any course chip. One is still open - see the Shared Maps tab.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Courses carrying an ask in their history</t>
   </si>
   <si>
@@ -114,7 +137,13 @@
     <t xml:space="preserve">  -&gt; still blocked on us</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleared. Every remaining open item needs Kevin on a golf course.</t>
+    <t xml:space="preserve">Cleared.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shared-map groups still open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 cards still share a byte-identical map. Was 143 groups on 2026-08-12. See the Shared Maps tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-check — rows actually present on each tab</t>
@@ -132,6 +161,9 @@
     <t xml:space="preserve">Verified Closed rows</t>
   </si>
   <si>
+    <t xml:space="preserve">Shared Maps rows</t>
+  </si>
+  <si>
     <t xml:space="preserve">DONE 2026-09-01 — five of the six courses on the 'Kevin - To Do' tab are currently marked RESOLVED in the queue, so they did NOT appear on Kevin's list. They were closed in earlier sessions but live data shows the work was never finished, so all five were REOPENED as Code Review Reject — the only status that keeps a course in the incomplete working list (v1072) as well as on the sent-back chip. Each carries a written note explaining why.</t>
   </si>
   <si>
@@ -919,6 +951,165 @@
   </si>
   <si>
     <t xml:space="preserve">Tracked under cr-mrdc3ito-o4ff9 — this entry is a duplicate filing, no separate work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still sharing one map — 17 groups, 34 cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found by re-running the detector from queue entry cr-sharedmap-siblings-20260812 on 2026-09-01: an md5 of every hole's green coordinate, over live cards only, tombstones excluded. That entry was filed 2026-08-12 with 143 groups and sent back on 16 Aug — but it has NO course attached, so it renders on nobody's list and has been invisible in the app since. 126 groups have been cleared since; these 17 have not. The 'first read' column is a judgement from the names alone and needs confirming before anything is deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The two cards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Course IDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First read — needs confirming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcadia Bluffs - Bluffs Course / Arcadia Bluffs Golf Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arcadia-bluffs-golf-club | arcadia-bluffs-mi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads like the same course listed twice under two names — a rename or an import duplicate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tombstone one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Campanas - Sunset / Las Campanas Sunset Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">las-campanas-sunset-course | the-club-at-las-campanas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauna Lani - South / Mauna Lani Resort South Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mauna-lani-golf | mauna-lani-resort-south-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasatch Mountain SP - Lake (listed twice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lake-at-wasatch-mountain-state-park | wasatch-mountain-state-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponkapoag #1 (listed twice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-at-ponkapoag-golf-club | ponkapoag-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crestview CC - North / North at Crestview CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crestview-country-club | north-at-crestview-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalina Saddlebrooke (listed twice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">catalina-saddlebrooke-at-saddlebrooke-country-cl | tucson-catalina-at-saddlebrooke-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spanish Peaks Toms 10 / The Club at Spanish Peaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spanish-peaks-mountain-club-toms-10-golf-course | the-club-at-spanish-peaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentwater - Grand Pines / Grand Pines Golf Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bentwater-grand-pines | grand-pines-golf-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brae Burn CC (Highland) / Highland at Brae Burn CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brae-burn-country-club | highland-at-brae-burn-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etowah Valley CC / Etowah Valley Golf &amp; Resort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etowah-valley-country-club | etowah-valley-golf-resort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads like the same course listed twice under two names — a rename or an import duplicate. NOTE Etowah Valley has three nines, so check this is not really a multi-nine wiring job.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tombstone one, or wire the nines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmetto Dunes - Arthur Hills / Palmetto Dunes - George Fazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palmetto-dunes-arthur-hills-golf-course | palmetto-dunes-george-fazio-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. These are two well-known, separate 18s at the same resort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-map one on site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hideaway East / Hideaway West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hideaway-east | hideaway-west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. East and West are different courses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emporia Country Club / Emporia Municipal Golf Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emporia-country-club | emporia-municipal-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. A private club and a muni in the same town are not the same golf course.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Havasu Golf Course / London Bridge Golf Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lake-havasu-golf-course | london-bridge-golf-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. Two separate clubs in Lake Havasu City.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deerfield CC / Deerfield CC East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deerfield-country-club | deerfield-country-club-east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. Deerfield is already wired as a three-nine facility, so the East card may be a stray.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the wiring first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverly Park Golf Course / Beverly Park Junior Golf Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beverly-park-golf-course | beverly-park-junior-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. A course and its junior course are different layouts.</t>
   </si>
 </sst>
 </file>
@@ -1251,6 +1442,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1431,7 +1626,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -1519,7 +1714,7 @@
       <c r="A10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1551,112 +1746,182 @@
       <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="10" t="n">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="10" t="n">
+      <c r="C22" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B21" s="12" t="n">
+      <c r="C23" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="12" t="n">
         <f aca="false">COUNTA('Kevin - To Do'!A5:A200)</f>
         <v>6</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="12" t="n">
+      <c r="C28" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="12" t="n">
         <f aca="false">COUNTA('Fixed By Us'!A5:A200)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="12" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="12" t="n">
         <f aca="false">COUNTA('Verified Closed'!A5:A200)</f>
         <v>38</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="12" t="n">
+        <f aca="false">COUNTA('Shared Maps'!A5:A200)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:C27"/>
+    <mergeCell ref="A34:C36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1687,41 +1952,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1729,28 +1994,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1758,28 +2023,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1787,28 +2052,28 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1816,28 +2081,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1845,28 +2110,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1874,28 +2139,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -1929,38 +2194,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1968,25 +2233,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1994,25 +2259,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2020,25 +2285,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2046,25 +2311,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2072,25 +2337,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2123,675 +2388,675 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -2805,4 +3070,403 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:F21"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/qa/BadGolf_CodeReviewQueue_Open_Items_2026-09-01.xlsx
+++ b/qa/BadGolf_CodeReviewQueue_Open_Items_2026-09-01.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Fixed By Us'!$A$4:$H$9</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Kevin - To Do'!$A$4:$I$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Kevin - To Do'!$A$4:$I$14</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Shared Maps'!$A$4:$F$21</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Verified Closed'!$A$4:$E$42</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="405">
   <si>
     <t xml:space="preserve">Bad Golf — Code Review Queue status</t>
   </si>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">Rejected / sent back</t>
   </si>
   <si>
-    <t xml:space="preserve">Historical FILINGS, not open items — breakdown below. They span 173 distinct courses.</t>
+    <t xml:space="preserve">Historical FILINGS, not open items - breakdown below. They span 173 distinct courses.</t>
   </si>
   <si>
     <t xml:space="preserve">Still NEW (open on Kevin's list)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hickory Sticks — the Meadows nine needs an on-course map.</t>
+    <t xml:space="preserve">Hickory Sticks (Meadows) and Pine Orchard - Kevin is working Pine Orchard now.</t>
   </si>
   <si>
     <t xml:space="preserve">Sent back to Kevin today</t>
   </si>
   <si>
-    <t xml:space="preserve">Reopened as Code Review Reject: Sonny Guy, Viewpoint, Weekapaug, The Glen, Pine Orchard.</t>
+    <t xml:space="preserve">5 reopened this morning, plus 4 from the shared-map audit.</t>
   </si>
   <si>
     <t xml:space="preserve">Courses on Kevin's list in the app</t>
   </si>
   <si>
-    <t xml:space="preserve">1 in review + 5 sent back. The dashboard 'Code Review Reject' chip should now read 5, not 0.</t>
+    <t xml:space="preserve">2 in review + 4 sent back. Kevin cleared 4 of the 5 reopened between 19:42 and 19:57.</t>
   </si>
   <si>
     <t xml:space="preserve">Cleared in this session</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">  -&gt; still blocked on us</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleared.</t>
+    <t xml:space="preserve">Cleared again - SaddleBrooke is wired.</t>
   </si>
   <si>
     <t xml:space="preserve">Shared-map groups still open</t>
   </si>
   <si>
-    <t xml:space="preserve">34 cards still share a byte-identical map. Was 143 groups on 2026-08-12. See the Shared Maps tab.</t>
+    <t xml:space="preserve">Was 143 on 2026-08-12 and 17 this morning. The detector now returns zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Cross-check — rows actually present on each tab</t>
@@ -215,13 +215,37 @@
     <t xml:space="preserve">NEW (open)</t>
   </si>
   <si>
-    <t xml:space="preserve">The Meadows nine has NO greens. It previously held a copy of the Mounds nine — every green within an average of 3 m of the matching Mounds green — so it was cleared rather than point players at the wrong putting surfaces.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map the MEADOWS nine only: 9 greens + fairway targets. Do NOT remap Mounds or Woods, both are correct. If greens appear already placed when you open Meadows, that is the app bug — clear the hole and drop it yourself.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live count: meadows = 0 greens; mounds = 9; woods = 9. Woods sits 774 m from Mounds, so it is genuinely a different nine and is fine.</t>
+    <t xml:space="preserve">The Meadows nine has NO greens. It previously held a copy of the Mounds nine (every green within an average of 3 m of the matching Mounds green), so it was cleared rather than point players at the wrong putting surfaces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map the MEADOWS nine only: 9 greens + fairway targets. Do NOT remap Mounds or Woods, both are correct. If greens appear already placed when you open Meadows, that is the app bug - clear the hole and drop it yourself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live count: meadows = 0 greens; mounds = 9; woods = 9.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pine Orchard Yacht &amp; Country Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branford, CT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine-orchard-yacht-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-recon26-f6036d4fac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW - Kevin working it (19:51 today)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 pins but only 16 distinct positions, so two greens still share a position with another hole. Was 15 distinct when first flagged on 2026-08-26.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the two holes whose pin sits on another hole's green and drop each on its own. The scorecard is correct - 18 genuinely different holes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-checked 2026-09-01 20:30: still 18 pins / 16 distinct. The GPS row was touched at 19:51 today, so this one is in progress.</t>
   </si>
   <si>
     <t xml:space="preserve">Sonny Guy Golf Course</t>
@@ -236,16 +260,16 @@
     <t xml:space="preserve">cr-wrongmap-sonny-guy-golf-course</t>
   </si>
   <si>
-    <t xml:space="preserve">REOPENED 2026-09-01 — Code Review Reject (sent back)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Still mapped onto a different golf course. All 18 of its greens sit within 40 m of Pete Brown Golf Facility's greens. This was flagged 2026-08-18 and was never actually fixed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Map all 18 holes on site, on Sonny Guy's own greens. If it turns out this entry IS Pete Brown Golf Facility under another name, say so and we will delete the duplicate instead of mapping it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-ran the overlap scan today: 18 of 18 greens still match pete-brown-golf-facility within 40 m.</t>
+    <t xml:space="preserve">Kevin marked RESOLVED - not yet verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 18 greens still sit within 40 m of Pete Brown Golf Facility's greens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map all 18 holes on Sonny Guy's own greens. If this entry IS Pete Brown under another name, say so and we delete the duplicate instead.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GPS row was edited at 19:46 today and the flag cleared, but the overlap is UNCHANGED - 18 of 18 greens still match Pete Brown. Worth confirming before this is treated as done.</t>
   </si>
   <si>
     <t xml:space="preserve">Viewpoint Golf Resort</t>
@@ -260,13 +284,34 @@
     <t xml:space="preserve">cr-wrongmap-viewpoint-golf-resort</t>
   </si>
   <si>
-    <t xml:space="preserve">Half of it is still mapped onto the neighbouring course. 9 of its 18 greens sit within 40 m of Championship At Viewpoint Golf Resort's greens. Partially fixed since 2026-08-18, never finished.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walk the course and re-drop the 9 holes that are wrong. The other 9 are already on their own greens — check each hole against what the app shows before re-dropping.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-ran the overlap scan today: 9 of 18 greens still match championship-at-viewpoint-golf-resort within 40 m.</t>
+    <t xml:space="preserve">9 of 18 greens still sit within 40 m of Championship At Viewpoint's greens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-drop the nine holes that are still wrong. The other nine are already right - check each against the app before re-dropping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GPS row was edited at 19:57 today and the flag cleared, but 9 of 18 greens still overlap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Glen Golf Park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madison, WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the-glen-golf-park</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-recon26-03845cef62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The card is a nine played twice (par 4-3-3-4-4-3-4-3-4). The mapped back nine reads 4-4-4-3-4-4-5-5-5, which is a different golf course.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-map holes 10-18 on The Glen's own greens, matching holes 1-9 hole for hole. Or tell us the card is wrong and we will replace it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The GPS row was edited at 19:42 today and the flag cleared, but the back-nine pars are unchanged and 0 of 9 back pins match a front pin.</t>
   </si>
   <si>
     <t xml:space="preserve">Weekapaug Golf Club</t>
@@ -281,55 +326,106 @@
     <t xml:space="preserve">cr-recon26-c7b9a50406</t>
   </si>
   <si>
-    <t xml:space="preserve">Weekapaug is a nine played twice, and the card says so. Holes 10-18 hold the right greens but in a rotated order, so the pars land on the wrong holes. Flagged 2026-08-26, never fixed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-drop holes 10-18 so each one sits on the SAME green as the matching hole 1-9: hole 10 = hole 1's green, hole 11 = hole 2's green, and so on through 18 = 9.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 of 9 back-nine pins currently match their front-nine partner. Mapped front pars read 4-4-3-4-5-4-4-3-5 (correct); mapped back pars read 4-4-3-5-4-5-3-4-4 (rotated).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Glen Golf Park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madison, WI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">the-glen-golf-park</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr-recon26-03845cef62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The card is a nine played twice (par 4-3-3-4-4-3-4-3-4, par 32 each way). The mapped back nine reads par 4-4-4-3-4-4-5-5-5 — that is a different golf course entirely. Flagged 2026-08-26, never fixed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-map holes 10-18 on The Glen's own greens, matching holes 1-9 hole for hole. If you believe the scorecard is the thing that is wrong, tell us and we will replace the card instead.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mapped front pars match the stored card exactly (4-3-3-4-4-3-4-3-4). Back nine matches neither the card nor the front nine; 0 of 9 back pins match a front pin.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pine Orchard Yacht &amp; Country Club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branford, CT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine-orchard-yacht-country-club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cr-recon26-f6036d4fac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 pins but only 16 distinct positions — two greens are still sitting on top of another hole's green. Was 15 distinct when flagged on 2026-08-26, so it was partly fixed and then left.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Find the two holes whose pin sits on another hole's green and drop each on its own green. The scorecard is correct — 18 real holes, all different — so every pin should be its own position.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Live count today: 18 pins, 16 distinct green coordinates. Only 2 of the back-nine pins coincide with a front-nine pin.</t>
+    <t xml:space="preserve">A nine played twice, but holes 10-18 hold the right greens in a rotated order, so six of nine pars land on the wrong hole.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-drop holes 10-18 so each sits on the SAME green as the matching hole 1-9.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The flag was cleared, but this GPS row has NOT been touched since 2026-07-20 and still reads source 'osm'. 0 of 9 back pins match their front partner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emporia Country Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emporia, KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emporia-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-sharedmap-emporia-cc-20260901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent back today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A NINE-hole club that was carrying an EIGHTEEN-green map, and that map is Emporia Municipal's. Its 18-hole par row fits the ground hole for hole; the CC's nine-hole card fits it nowhere. The wrong map has been removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map Emporia Country Club's own nine on site: 9 greens + fairway targets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par fit: the four short holes land on Municipal's four par 3s (216, 169, 207, 165 yd) and the three long ones on its par 5s (542, 491, 501 yd).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmetto Dunes - George Fazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hilton Head Island, SC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palmetto-dunes-george-fazio-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-sharedmap-pd-fazio-20260901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazio and Arthur Hills were sharing one set of greens. The map is ARTHUR HILLS' - its par row fits hole for hole. Fazio is the resort's par 70 and fits nowhere. The wrong map has been removed from the Fazio card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map the George Fazio course on site: 18 greens + fairway targets.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par fit: short holes on Arthur Hills' par 3s (139, 133, 170, 154 yd), long ones on its par 5s (489, 506, 494 yd). Fazio's own card is correct and untouched.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London Bridge Golf Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Havasu City, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">london-bridge-golf-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-sharedmap-london-bridge-20260901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent back today - needs a decision first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was sharing Lake Havasu Golf Course's greens, AND its par row is a byte-for-byte copy of Lake Havasu's. Its only rating is a lone 76.9 with no tee name. Both the map and the scorecard came from the other club. The wrong map has been removed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First tell us: is London Bridge genuinely a separate course from Lake Havasu Golf Course, or two names for one place? If separate it needs its own card and its own map; if the same, we merge and delete the duplicate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The map fits the shared par row exactly (par 3s at 207, 158, 167, 160 yd; par 5s at 511, 482, 488 yd), so the greens are Lake Havasu's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaddleBrooke Country Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucson, AZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tucson-catalina-at-saddlebrooke-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cr-sharedmap-saddlebrooke-20260901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now wired as the 27-hole club it actually is (Tucson, Catalina, SaddleBrooke). It had been two 18-hole combination cards both pointing at one eighteen-green map; that map is Tucson 1-9 + Catalina 10-18 and has been split. The SADDLEBROOKE nine has no greens at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map the SADDLEBROOKE nine only: 9 greens + fairway targets. Do NOT remap Tucson or Catalina, both are correct. Note the club prints the front nine on the EVEN handicap numbers and the back nine on the ODD ones - that is stored and handled, it just looks inverted next to other courses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map fit is exact on both halves (Tucson holes 1-9 measured 420/213/493... against a card of 418/211/513...; Catalina 437/372/191... against 438/377/192...). All three combination ratings reconcile to the club's published yardages.</t>
   </si>
   <si>
     <t xml:space="preserve">Blocked on us — all cleared 2026-09-01</t>
@@ -578,9 +674,6 @@
     <t xml:space="preserve">Pusch Ridge Golf Course</t>
   </si>
   <si>
-    <t xml:space="preserve">Tucson, AZ</t>
-  </si>
-  <si>
     <t xml:space="preserve">pusch-ridge-golf-course-hilton-tucson-el-conquis</t>
   </si>
   <si>
@@ -953,13 +1046,13 @@
     <t xml:space="preserve">Tracked under cr-mrdc3ito-o4ff9 — this entry is a duplicate filing, no separate work.</t>
   </si>
   <si>
-    <t xml:space="preserve">Still sharing one map — 17 groups, 34 cards</t>
+    <t xml:space="preserve">Shared maps - all 17 groups cleared</t>
   </si>
   <si>
     <t xml:space="preserve">Found by re-running the detector from queue entry cr-sharedmap-siblings-20260812 on 2026-09-01: an md5 of every hole's green coordinate, over live cards only, tombstones excluded. That entry was filed 2026-08-12 with 143 groups and sent back on 16 Aug — but it has NO course attached, so it renders on nobody's list and has been invisible in the app since. 126 groups have been cleared since; these 17 have not. The 'first read' column is a judgement from the names alone and needs confirming before anything is deleted.</t>
   </si>
   <si>
-    <t xml:space="preserve">The two cards</t>
+    <t xml:space="preserve">Facility</t>
   </si>
   <si>
     <t xml:space="preserve">Course IDs</t>
@@ -968,148 +1061,190 @@
     <t xml:space="preserve">Greens</t>
   </si>
   <si>
-    <t xml:space="preserve">First read — needs confirming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likely action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arcadia Bluffs - Bluffs Course / Arcadia Bluffs Golf Club</t>
+    <t xml:space="preserve">What it turned out to be</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result 2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcadia Bluffs - Bluffs Course</t>
   </si>
   <si>
     <t xml:space="preserve">arcadia-bluffs-golf-club | arcadia-bluffs-mi</t>
   </si>
   <si>
-    <t xml:space="preserve">Reads like the same course listed twice under two names — a rename or an import duplicate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tombstone one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Campanas - Sunset / Las Campanas Sunset Course</t>
+    <t xml:space="preserve">Same course filed twice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the 10-tee card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ponkapoag Golf Course #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-at-ponkapoag-golf-club | ponkapoag-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the 4-tee card, renamed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentwater - Grand Pines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bentwater-grand-pines | grand-pines-golf-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same course twice; one card had two UNRATED tees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the fully-rated card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brae Burn CC (Highland)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brae-burn-country-club | highland-at-brae-burn-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same nine twice; one card carried 18-hole ratings on a 9-hole par row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the correct 9-hole card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crestview CC - North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crestview-country-club | north-at-crestview-country-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the 5-tee card, renamed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etowah Valley Country Club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">etowah-valley-country-club | etowah-valley-golf-resort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same course twice; one card had a single tee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the 5-tee card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wasatch Mountain SP - Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lake-at-wasatch-mountain-state-park | wasatch-mountain-state-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERGED - kept the 3-tee card, renamed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Campanas - Sunset</t>
   </si>
   <si>
     <t xml:space="preserve">las-campanas-sunset-course | the-club-at-las-campanas</t>
   </si>
   <si>
-    <t xml:space="preserve">Mauna Lani - South / Mauna Lani Resort South Course</t>
+    <t xml:space="preserve">MERGED - kept the explicit course card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mauna Lani Resort - South</t>
   </si>
   <si>
     <t xml:space="preserve">mauna-lani-golf | mauna-lani-resort-south-course</t>
   </si>
   <si>
-    <t xml:space="preserve">Wasatch Mountain SP - Lake (listed twice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lake-at-wasatch-mountain-state-park | wasatch-mountain-state-golf-course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ponkapoag #1 (listed twice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1-at-ponkapoag-golf-club | ponkapoag-golf-course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crestview CC - North / North at Crestview CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crestview-country-club | north-at-crestview-country-club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalina Saddlebrooke (listed twice)</t>
+    <t xml:space="preserve">The Club at Spanish Peaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spanish-peaks-mountain-club-toms-10-golf-course | the-club-at-spanish-peaks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deerfield CC East</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deerfield-country-club | deerfield-country-club-east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A stray nine card on a facility already wired as a three-nine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMBSTONED the stray card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverly Park Golf Course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beverly-park-golf-course | beverly-park-junior-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same par-3 nine twice - identical greens and pars, and the junior card's 24.0 rating is not credible for the 1,069 yd on the ground.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMBSTONED the junior card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hide-A-Way Lake Club East / West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hideaway-east | hideaway-west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two NINE-hole cards both pointing at one EIGHTEEN-green map. That map turned out to be West holes 1-9 + East holes 10-18; the par fit is exact on both halves.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIXED - split, each nine now has its own 9 greens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emporia CC / Emporia Municipal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emporia-country-club | emporia-municipal-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuinely different courses. The map is the Municipal's; the CC is a nine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map CLEARED, sent back to Kevin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palmetto Dunes Arthur Hills / George Fazio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palmetto-dunes-arthur-hills-golf-course | palmetto-dunes-george-fazio-golf-course</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genuinely different courses. The map is Arthur Hills'; Fazio is the par 70.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fazio map CLEARED, sent back to Kevin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lake Havasu / London Bridge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lake-havasu-golf-course | london-bridge-golf-club</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London Bridge carried Lake Havasu's map AND a byte-copy of its par row, plus a lone uncredible 76.9 rating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map CLEARED, sent back - needs a same-or-different decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaddleBrooke CC - Tucson / Catalina / SaddleBrooke</t>
   </si>
   <si>
     <t xml:space="preserve">catalina-saddlebrooke-at-saddlebrooke-country-cl | tucson-catalina-at-saddlebrooke-country-club</t>
   </si>
   <si>
-    <t xml:space="preserve">Spanish Peaks Toms 10 / The Club at Spanish Peaks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spanish-peaks-mountain-club-toms-10-golf-course | the-club-at-spanish-peaks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentwater - Grand Pines / Grand Pines Golf Club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bentwater-grand-pines | grand-pines-golf-club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brae Burn CC (Highland) / Highland at Brae Burn CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brae-burn-country-club | highland-at-brae-burn-country-club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etowah Valley CC / Etowah Valley Golf &amp; Resort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">etowah-valley-country-club | etowah-valley-golf-resort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reads like the same course listed twice under two names — a rename or an import duplicate. NOTE Etowah Valley has three nines, so check this is not really a multi-nine wiring job.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tombstone one, or wire the nines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palmetto Dunes - Arthur Hills / Palmetto Dunes - George Fazio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palmetto-dunes-arthur-hills-golf-course | palmetto-dunes-george-fazio-golf-course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. These are two well-known, separate 18s at the same resort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-map one on site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hideaway East / Hideaway West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hideaway-east | hideaway-west</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. East and West are different courses.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emporia Country Club / Emporia Municipal Golf Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emporia-country-club | emporia-municipal-golf-course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. A private club and a muni in the same town are not the same golf course.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lake Havasu Golf Course / London Bridge Golf Club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lake-havasu-golf-course | london-bridge-golf-club</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. Two separate clubs in Lake Havasu City.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deerfield CC / Deerfield CC East</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deerfield-country-club | deerfield-country-club-east</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. Deerfield is already wired as a three-nine facility, so the East card may be a stray.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the wiring first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverly Park Golf Course / Beverly Park Junior Golf Course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beverly-park-golf-course | beverly-park-junior-golf-course</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two genuinely DIFFERENT courses sharing one map — one is mapped onto the other. Whichever is wrong needs re-mapping on site. A course and its junior course are different layouts.</t>
+    <t xml:space="preserve">NOT a duplicate: two 18-hole COMBINATIONS of the same 27 holes. Measuring the shared map showed it is Tucson holes 1-9 + Catalina holes 10-18, so one card was carrying it wrongly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WIRED as a 27-hole facility; map split to #tucson and #catalina; duplicate card tombstoned</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1795,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>6</v>
@@ -1671,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>8</v>
@@ -1682,7 +1817,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>10</v>
@@ -1693,18 +1828,18 @@
         <v>11</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>14</v>
@@ -1847,12 +1982,12 @@
       <c r="B24" s="9"/>
       <c r="C24" s="6"/>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>37</v>
@@ -1869,7 +2004,7 @@
       </c>
       <c r="B28" s="12" t="n">
         <f aca="false">COUNTA('Kevin - To Do'!A5:A200)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>40</v>
@@ -1938,7 +2073,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2064,16 +2199,16 @@
         <v>75</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2081,28 +2216,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2110,28 +2245,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2139,32 +2274,148 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="117.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I10"/>
+  <autoFilter ref="A4:I14"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2194,12 +2445,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2219,13 +2470,13 @@
         <v>51</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2233,25 +2484,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2259,25 +2510,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2285,25 +2536,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2311,25 +2562,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2337,25 +2588,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2388,12 +2639,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2407,656 +2658,656 @@
         <v>50</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="D13" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>188</v>
+        <v>219</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>190</v>
+        <v>221</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>207</v>
+        <v>238</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>214</v>
+        <v>245</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>216</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>219</v>
+        <v>250</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>220</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>224</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>229</v>
+        <v>260</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>228</v>
+        <v>259</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>232</v>
+        <v>263</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>290</v>
+        <v>321</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>300</v>
+        <v>331</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3090,12 +3341,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>308</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3103,19 +3354,19 @@
         <v>47</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>310</v>
+        <v>341</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>311</v>
+        <v>342</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3123,19 +3374,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>315</v>
+        <v>346</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3143,19 +3394,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3163,19 +3414,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>316</v>
+        <v>354</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>317</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3183,19 +3434,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>322</v>
+        <v>356</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>323</v>
+        <v>357</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>316</v>
+        <v>358</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>317</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3203,19 +3454,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3223,19 +3474,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>326</v>
+        <v>363</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>316</v>
+        <v>365</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>317</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3243,19 +3494,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>317</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3263,19 +3514,19 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>331</v>
+        <v>371</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>317</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3283,19 +3534,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3303,19 +3554,19 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>316</v>
+        <v>347</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>317</v>
+        <v>362</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3323,19 +3574,19 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3343,19 +3594,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3363,19 +3614,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>343</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3383,19 +3634,19 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>348</v>
+        <v>390</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>349</v>
+        <v>391</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>343</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3403,19 +3654,19 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3423,19 +3674,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>353</v>
+        <v>397</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>356</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3443,19 +3694,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>357</v>
+        <v>401</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>358</v>
+        <v>402</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>359</v>
+        <v>403</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>343</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
